--- a/output/Data and Chart Outputs/china_nbs_energy_production_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_energy_production_monthly.xlsx
@@ -25,9 +25,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -67,13 +68,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -167,6 +167,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -323,11 +324,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -355,14 +368,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -393,6 +414,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -442,11 +464,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -474,15 +508,19 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -512,6 +550,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -561,11 +600,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -593,15 +644,19 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -631,6 +686,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -716,11 +772,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -748,14 +816,22 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -786,6 +862,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -835,11 +912,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -867,15 +956,19 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -905,6 +998,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <lineChart>
@@ -954,11 +1048,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="4"/>
@@ -986,15 +1092,19 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -1485,6 +1595,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -1499,6 +1610,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -1513,6 +1625,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1527,6 +1640,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -1929,7 +2043,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -1949,7 +2063,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -1969,7 +2083,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -1989,7 +2103,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -2009,7 +2123,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -2029,7 +2143,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -2049,7 +2163,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -2069,7 +2183,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -2089,7 +2203,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -2109,7 +2223,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -2129,7 +2243,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -2149,7 +2263,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -2169,7 +2283,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -2189,7 +2303,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -2209,7 +2323,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -2229,7 +2343,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -2249,7 +2363,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -2269,7 +2383,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -2289,7 +2403,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -2309,7 +2423,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -2329,7 +2443,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -2349,7 +2463,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -2369,7 +2483,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -2389,7 +2503,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -2409,7 +2523,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -2429,7 +2543,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -2449,7 +2563,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -2469,7 +2583,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -2489,7 +2603,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -2509,7 +2623,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -2529,7 +2643,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -2549,7 +2663,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -2569,7 +2683,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -2589,7 +2703,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -2609,7 +2723,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -2629,7 +2743,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -2649,7 +2763,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -2669,7 +2783,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -2689,7 +2803,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -2709,7 +2823,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -2729,7 +2843,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -2749,7 +2863,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -2769,7 +2883,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -2789,7 +2903,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -2809,7 +2923,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -2829,7 +2943,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -2849,7 +2963,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -2869,7 +2983,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -2889,7 +3003,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -2909,7 +3023,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -2929,7 +3043,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -2949,7 +3063,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -2969,7 +3083,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -2989,7 +3103,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -3009,7 +3123,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -3029,7 +3143,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -3079,7 +3193,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -3087,7 +3201,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -3095,7 +3209,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -3103,7 +3217,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -3111,7 +3225,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -3119,7 +3233,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -3127,7 +3241,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -3135,7 +3249,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -3143,7 +3257,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -3151,7 +3265,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -3159,7 +3273,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -3167,7 +3281,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -3175,7 +3289,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -3183,7 +3297,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -3191,7 +3305,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -3199,7 +3313,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -3207,7 +3321,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -3215,7 +3329,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -3223,7 +3337,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -3231,7 +3345,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -3239,7 +3353,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -3247,7 +3361,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -3255,7 +3369,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -3263,7 +3377,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -3271,7 +3385,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -3279,7 +3393,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -3287,7 +3401,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -3295,7 +3409,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -3303,7 +3417,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -3311,7 +3425,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -3319,7 +3433,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -3327,7 +3441,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -3335,7 +3449,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -3343,7 +3457,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -3351,7 +3465,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -3359,7 +3473,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -3367,7 +3481,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -3375,7 +3489,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -3383,7 +3497,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -3391,7 +3505,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -3399,7 +3513,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -3407,7 +3521,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -3415,7 +3529,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -3423,7 +3537,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -3431,7 +3545,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -3439,7 +3553,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -3447,7 +3561,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -3455,7 +3569,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -3463,7 +3577,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -3471,7 +3585,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -3479,7 +3593,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -3487,7 +3601,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -3495,7 +3609,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -3503,7 +3617,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -3511,7 +3625,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -3519,7 +3633,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -3557,7 +3671,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -3565,7 +3679,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -3573,7 +3687,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -3581,7 +3695,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -3589,7 +3703,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -3597,7 +3711,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -3605,7 +3719,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -3613,7 +3727,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -3621,7 +3735,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -3629,7 +3743,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -3637,7 +3751,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -3645,7 +3759,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -3653,7 +3767,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -3661,7 +3775,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -3669,7 +3783,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -3677,7 +3791,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -3685,7 +3799,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -3693,7 +3807,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -3701,7 +3815,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -3709,7 +3823,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -3717,7 +3831,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -3725,7 +3839,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -3733,7 +3847,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -3741,7 +3855,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -3749,7 +3863,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -3757,7 +3871,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -3765,7 +3879,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -3773,7 +3887,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -3781,7 +3895,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -3789,7 +3903,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -3797,7 +3911,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -3805,7 +3919,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -3813,7 +3927,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -3821,7 +3935,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -3829,7 +3943,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -3837,7 +3951,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -3845,7 +3959,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -3853,7 +3967,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -3861,7 +3975,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -3869,7 +3983,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -3877,7 +3991,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -3885,7 +3999,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -3893,7 +4007,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -3901,7 +4015,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -3909,7 +4023,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -3917,7 +4031,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -3925,7 +4039,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -3933,7 +4047,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -3941,7 +4055,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -3949,7 +4063,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -3957,7 +4071,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -3965,7 +4079,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -3973,7 +4087,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -3981,7 +4095,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -3989,7 +4103,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -3997,7 +4111,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -4040,7 +4154,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -4051,7 +4165,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -4062,7 +4176,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -4073,7 +4187,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -4084,7 +4198,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -4095,7 +4209,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -4106,7 +4220,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -4117,7 +4231,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -4128,7 +4242,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -4139,7 +4253,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -4150,7 +4264,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -4161,7 +4275,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -4172,7 +4286,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -4183,7 +4297,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -4194,7 +4308,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -4205,7 +4319,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -4216,7 +4330,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -4227,7 +4341,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -4238,7 +4352,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -4249,7 +4363,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -4260,7 +4374,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -4271,7 +4385,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -4282,7 +4396,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -4293,7 +4407,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -4304,7 +4418,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -4315,7 +4429,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -4326,7 +4440,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -4337,7 +4451,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -4348,7 +4462,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -4359,7 +4473,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -4370,7 +4484,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -4381,7 +4495,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -4392,7 +4506,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -4403,7 +4517,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -4414,7 +4528,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -4425,7 +4539,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -4436,7 +4550,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -4447,7 +4561,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -4458,7 +4572,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -4469,7 +4583,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -4480,7 +4594,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -4491,7 +4605,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -4502,7 +4616,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -4513,7 +4627,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -4524,7 +4638,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -4535,7 +4649,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -4546,7 +4660,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -4557,7 +4671,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -4568,7 +4682,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -4579,7 +4693,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -4590,7 +4704,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -4601,7 +4715,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -4612,7 +4726,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -4623,7 +4737,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -4634,7 +4748,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -4645,7 +4759,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -4686,7 +4800,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -4694,7 +4808,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -4702,7 +4816,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -4710,7 +4824,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -4718,7 +4832,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -4726,7 +4840,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -4734,7 +4848,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -4742,7 +4856,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -4750,7 +4864,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -4758,7 +4872,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -4766,7 +4880,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -4774,7 +4888,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -4782,7 +4896,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -4790,7 +4904,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -4798,7 +4912,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -4806,7 +4920,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -4814,7 +4928,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -4822,7 +4936,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -4830,7 +4944,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -4838,7 +4952,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -4846,7 +4960,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -4854,7 +4968,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -4862,7 +4976,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -4870,7 +4984,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -4878,7 +4992,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -4886,7 +5000,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -4894,7 +5008,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -4902,7 +5016,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -4910,7 +5024,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -4918,7 +5032,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -4926,7 +5040,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -4934,7 +5048,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -4942,7 +5056,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -4950,7 +5064,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -4958,7 +5072,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -4966,7 +5080,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -4974,7 +5088,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -4982,7 +5096,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -4990,7 +5104,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -4998,7 +5112,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -5006,7 +5120,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -5014,7 +5128,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -5022,7 +5136,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -5030,7 +5144,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -5038,7 +5152,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -5046,7 +5160,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -5054,7 +5168,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -5062,7 +5176,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -5070,7 +5184,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -5078,7 +5192,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -5086,7 +5200,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -5094,7 +5208,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -5102,7 +5216,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -5110,7 +5224,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -5118,7 +5232,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -5126,7 +5240,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">
@@ -5164,7 +5278,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B2" t="n">
@@ -5172,7 +5286,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>44287</v>
       </c>
       <c r="B3" t="n">
@@ -5180,7 +5294,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>44317</v>
       </c>
       <c r="B4" t="n">
@@ -5188,7 +5302,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>44348</v>
       </c>
       <c r="B5" t="n">
@@ -5196,7 +5310,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>44378</v>
       </c>
       <c r="B6" t="n">
@@ -5204,7 +5318,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>44409</v>
       </c>
       <c r="B7" t="n">
@@ -5212,7 +5326,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>44440</v>
       </c>
       <c r="B8" t="n">
@@ -5220,7 +5334,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>44470</v>
       </c>
       <c r="B9" t="n">
@@ -5228,7 +5342,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B10" t="n">
@@ -5236,7 +5350,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>44531</v>
       </c>
       <c r="B11" t="n">
@@ -5244,7 +5358,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>44621</v>
       </c>
       <c r="B12" t="n">
@@ -5252,7 +5366,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>44652</v>
       </c>
       <c r="B13" t="n">
@@ -5260,7 +5374,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>44682</v>
       </c>
       <c r="B14" t="n">
@@ -5268,7 +5382,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>44713</v>
       </c>
       <c r="B15" t="n">
@@ -5276,7 +5390,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>44743</v>
       </c>
       <c r="B16" t="n">
@@ -5284,7 +5398,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B17" t="n">
@@ -5292,7 +5406,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>44805</v>
       </c>
       <c r="B18" t="n">
@@ -5300,7 +5414,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>44835</v>
       </c>
       <c r="B19" t="n">
@@ -5308,7 +5422,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>44866</v>
       </c>
       <c r="B20" t="n">
@@ -5316,7 +5430,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>44896</v>
       </c>
       <c r="B21" t="n">
@@ -5324,7 +5438,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>44986</v>
       </c>
       <c r="B22" t="n">
@@ -5332,7 +5446,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>45017</v>
       </c>
       <c r="B23" t="n">
@@ -5340,7 +5454,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B24" t="n">
@@ -5348,7 +5462,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>45078</v>
       </c>
       <c r="B25" t="n">
@@ -5356,7 +5470,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>45108</v>
       </c>
       <c r="B26" t="n">
@@ -5364,7 +5478,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>45139</v>
       </c>
       <c r="B27" t="n">
@@ -5372,7 +5486,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>45170</v>
       </c>
       <c r="B28" t="n">
@@ -5380,7 +5494,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>45200</v>
       </c>
       <c r="B29" t="n">
@@ -5388,7 +5502,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>45231</v>
       </c>
       <c r="B30" t="n">
@@ -5396,7 +5510,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>45261</v>
       </c>
       <c r="B31" t="n">
@@ -5404,7 +5518,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>45352</v>
       </c>
       <c r="B32" t="n">
@@ -5412,7 +5526,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B33" t="n">
@@ -5420,7 +5534,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>45413</v>
       </c>
       <c r="B34" t="n">
@@ -5428,7 +5542,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>45444</v>
       </c>
       <c r="B35" t="n">
@@ -5436,7 +5550,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B36" t="n">
@@ -5444,7 +5558,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>45505</v>
       </c>
       <c r="B37" t="n">
@@ -5452,7 +5566,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>45536</v>
       </c>
       <c r="B38" t="n">
@@ -5460,7 +5574,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>45566</v>
       </c>
       <c r="B39" t="n">
@@ -5468,7 +5582,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>45597</v>
       </c>
       <c r="B40" t="n">
@@ -5476,7 +5590,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>45627</v>
       </c>
       <c r="B41" t="n">
@@ -5484,7 +5598,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>45717</v>
       </c>
       <c r="B42" t="n">
@@ -5492,7 +5606,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>45748</v>
       </c>
       <c r="B43" t="n">
@@ -5500,7 +5614,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>45778</v>
       </c>
       <c r="B44" t="n">
@@ -5508,7 +5622,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>45809</v>
       </c>
       <c r="B45" t="n">
@@ -5516,7 +5630,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>45839</v>
       </c>
       <c r="B46" t="n">
@@ -5524,7 +5638,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>45870</v>
       </c>
       <c r="B47" t="n">
@@ -5532,7 +5646,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B48" t="n">
@@ -5540,7 +5654,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>45931</v>
       </c>
       <c r="B49" t="n">
@@ -5548,7 +5662,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>45962</v>
       </c>
       <c r="B50" t="n">
@@ -5556,7 +5670,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B51" t="n">
@@ -5564,7 +5678,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>46082</v>
       </c>
       <c r="B52" t="n">
@@ -5572,7 +5686,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>46113</v>
       </c>
       <c r="B53" t="n">
@@ -5580,7 +5694,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>46143</v>
       </c>
       <c r="B54" t="n">
@@ -5588,7 +5702,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B55" t="n">
@@ -5596,7 +5710,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B56" t="n">
@@ -5604,7 +5718,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B57" t="n">

--- a/output/Data and Chart Outputs/china_nbs_energy_production_monthly.xlsx
+++ b/output/Data and Chart Outputs/china_nbs_energy_production_monthly.xlsx
@@ -170,7 +170,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China power generation by source (NBS) (to Aug/26)</a:t>
+              <a:t>China power generation by source (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -200,12 +200,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$127</f>
+              <f>'Chart'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$127</f>
+              <f>'Chart'!$B$2:$B$128</f>
             </numRef>
           </val>
         </ser>
@@ -228,12 +228,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$127</f>
+              <f>'Chart'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$127</f>
+              <f>'Chart'!$C$2:$C$128</f>
             </numRef>
           </val>
         </ser>
@@ -256,12 +256,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$127</f>
+              <f>'Chart'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$127</f>
+              <f>'Chart'!$D$2:$D$128</f>
             </numRef>
           </val>
         </ser>
@@ -284,12 +284,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$127</f>
+              <f>'Chart'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$127</f>
+              <f>'Chart'!$E$2:$E$128</f>
             </numRef>
           </val>
         </ser>
@@ -312,12 +312,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$127</f>
+              <f>'Chart'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$127</f>
+              <f>'Chart'!$F$2:$F$128</f>
             </numRef>
           </val>
         </ser>
@@ -418,7 +418,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China energy industries value added y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China energy industries value added y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -454,12 +454,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - energy industries value'!$A$2:$A$131</f>
+              <f>'Chart - energy industries value'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - energy industries value'!$B$2:$B$131</f>
+              <f>'Chart - energy industries value'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -490,12 +490,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - energy industries value'!$A$2:$A$131</f>
+              <f>'Chart - energy industries value'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - energy industries value'!$C$2:$C$131</f>
+              <f>'Chart - energy industries value'!$C$2:$C$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -526,12 +526,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - energy industries value'!$A$2:$A$131</f>
+              <f>'Chart - energy industries value'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - energy industries value'!$D$2:$D$131</f>
+              <f>'Chart - energy industries value'!$D$2:$D$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -631,7 +631,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China raw coal output (NBS) (to Aug/26)</a:t>
+              <a:t>China raw coal output (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -667,12 +667,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - raw coal output'!$A$2:$A$116</f>
+              <f>'Chart - raw coal output'!$A$2:$A$117</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - raw coal output'!$B$2:$B$116</f>
+              <f>'Chart - raw coal output'!$B$2:$B$117</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -768,7 +768,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China coke output (NBS) (to Aug/26)</a:t>
+              <a:t>China coke output (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -804,12 +804,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - coke output'!$A$2:$A$131</f>
+              <f>'Chart - coke output'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - coke output'!$B$2:$B$131</f>
+              <f>'Chart - coke output'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -905,7 +905,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China crude oil output and refinery runs (NBS) (to Aug/26)</a:t>
+              <a:t>China crude oil output and refinery runs (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -941,12 +941,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - crude oil output and re'!$A$2:$A$131</f>
+              <f>'Chart - crude oil output and re'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - crude oil output and re'!$B$2:$B$131</f>
+              <f>'Chart - crude oil output and re'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -977,12 +977,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - crude oil output and re'!$A$2:$A$131</f>
+              <f>'Chart - crude oil output and re'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - crude oil output and re'!$C$2:$C$131</f>
+              <f>'Chart - crude oil output and re'!$C$2:$C$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1082,7 +1082,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China natural gas output (NBS) (to Aug/26)</a:t>
+              <a:t>China natural gas output (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1118,12 +1118,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - natural gas output'!$A$2:$A$127</f>
+              <f>'Chart - natural gas output'!$A$2:$A$128</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - natural gas output'!$B$2:$B$127</f>
+              <f>'Chart - natural gas output'!$B$2:$B$128</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1219,7 +1219,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China electricity generation (total) (NBS) (to Aug/26)</a:t>
+              <a:t>China electricity generation (total) (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1255,12 +1255,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - electricity generation '!$A$2:$A$131</f>
+              <f>'Chart - electricity generation '!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - electricity generation '!$B$2:$B$131</f>
+              <f>'Chart - electricity generation '!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1356,7 +1356,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China power generation y/y by source (NBS) (to Aug/26)</a:t>
+              <a:t>China power generation y/y by source (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1392,12 +1392,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$B$2:$B$131</f>
+              <f>'Chart - power generation y-y by'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1428,12 +1428,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$C$2:$C$131</f>
+              <f>'Chart - power generation y-y by'!$C$2:$C$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1464,12 +1464,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$D$2:$D$131</f>
+              <f>'Chart - power generation y-y by'!$D$2:$D$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1500,12 +1500,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$E$2:$E$131</f>
+              <f>'Chart - power generation y-y by'!$E$2:$E$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1536,12 +1536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$F$2:$F$131</f>
+              <f>'Chart - power generation y-y by'!$F$2:$F$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1572,12 +1572,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - power generation y-y by'!$A$2:$A$131</f>
+              <f>'Chart - power generation y-y by'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - power generation y-y by'!$G$2:$G$131</f>
+              <f>'Chart - power generation y-y by'!$G$2:$G$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1677,7 +1677,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China fuel output y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China fuel output y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1713,12 +1713,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - fuel output y-y'!$A$2:$A$131</f>
+              <f>'Chart - fuel output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - fuel output y-y'!$B$2:$B$131</f>
+              <f>'Chart - fuel output y-y'!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1749,12 +1749,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - fuel output y-y'!$A$2:$A$131</f>
+              <f>'Chart - fuel output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - fuel output y-y'!$C$2:$C$131</f>
+              <f>'Chart - fuel output y-y'!$C$2:$C$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1785,12 +1785,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - fuel output y-y'!$A$2:$A$131</f>
+              <f>'Chart - fuel output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - fuel output y-y'!$D$2:$D$131</f>
+              <f>'Chart - fuel output y-y'!$D$2:$D$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1821,12 +1821,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - fuel output y-y'!$A$2:$A$131</f>
+              <f>'Chart - fuel output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - fuel output y-y'!$E$2:$E$131</f>
+              <f>'Chart - fuel output y-y'!$E$2:$E$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1857,12 +1857,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - fuel output y-y'!$A$2:$A$131</f>
+              <f>'Chart - fuel output y-y'!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - fuel output y-y'!$F$2:$F$131</f>
+              <f>'Chart - fuel output y-y'!$F$2:$F$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1962,7 +1962,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>China industrial value added y/y (NBS) (to Aug/26)</a:t>
+              <a:t>China industrial value added y/y (NBS) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1998,12 +1998,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - industrial value added '!$A$2:$A$131</f>
+              <f>'Chart - industrial value added '!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - industrial value added '!$B$2:$B$131</f>
+              <f>'Chart - industrial value added '!$B$2:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2034,12 +2034,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - industrial value added '!$A$2:$A$131</f>
+              <f>'Chart - industrial value added '!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - industrial value added '!$C$2:$C$131</f>
+              <f>'Chart - industrial value added '!$C$2:$C$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2070,12 +2070,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - industrial value added '!$A$2:$A$131</f>
+              <f>'Chart - industrial value added '!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - industrial value added '!$D$2:$D$131</f>
+              <f>'Chart - industrial value added '!$D$2:$D$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2106,12 +2106,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart - industrial value added '!$A$2:$A$131</f>
+              <f>'Chart - industrial value added '!$A$2:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart - industrial value added '!$E$2:$E$131</f>
+              <f>'Chart - industrial value added '!$E$2:$E$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2885,7 +2885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -5117,6 +5117,23 @@
       </c>
       <c r="E131" t="n">
         <v>4.9</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D132" t="n">
+        <v>6</v>
+      </c>
+      <c r="E132" t="n">
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
@@ -5131,7 +5148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D131"/>
+  <dimension ref="A1:D132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -6473,6 +6490,20 @@
       </c>
       <c r="D131" t="n">
         <v>4.9</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="C132" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D132" t="n">
+        <v>5.6</v>
       </c>
     </row>
   </sheetData>
@@ -6487,7 +6518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG131"/>
+  <dimension ref="A1:BG132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27684,6 +27715,185 @@
         <v>4.9</v>
       </c>
       <c r="BG131" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>512.9</v>
+      </c>
+      <c r="C132" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="D132" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="E132" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="F132" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G132" t="n">
+        <v>385.13</v>
+      </c>
+      <c r="H132" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="I132" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="J132" t="n">
+        <v>57.48</v>
+      </c>
+      <c r="K132" t="n">
+        <v>21</v>
+      </c>
+      <c r="L132" t="n">
+        <v>829.4</v>
+      </c>
+      <c r="M132" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="N132" t="n">
+        <v>4734.3</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P132" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>1033.9</v>
+      </c>
+      <c r="R132" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S132" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="T132" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="U132" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V132" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W132" t="n">
+        <v>802.2</v>
+      </c>
+      <c r="X132" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>549.7</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>3449.05</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>373.16</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>513.6</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>196.7</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>7491.6</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>-3.3</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG132" t="n">
         <v>5.8</v>
       </c>
     </row>
@@ -32224,7 +32434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B96"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32996,6 +33206,14 @@
         <v>46235</v>
       </c>
       <c r="B96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -33010,7 +33228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -35359,6 +35577,26 @@
       </c>
       <c r="F127" t="n">
         <v>70</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B128" t="n">
+        <v>512.9</v>
+      </c>
+      <c r="C128" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="D128" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="E128" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="F128" t="n">
+        <v>64.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -35373,7 +35611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -36309,6 +36547,14 @@
       </c>
       <c r="B116" t="n">
         <v>361.82</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B117" t="n">
+        <v>385.13</v>
       </c>
     </row>
   </sheetData>
@@ -36323,7 +36569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -37379,6 +37625,14 @@
       </c>
       <c r="B131" t="n">
         <v>39.92</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>39.04</v>
       </c>
     </row>
   </sheetData>
@@ -37393,7 +37647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C131"/>
+  <dimension ref="A1:C132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -38832,6 +39086,17 @@
       </c>
       <c r="C131" t="n">
         <v>59.07</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="C132" t="n">
+        <v>57.48</v>
       </c>
     </row>
   </sheetData>
@@ -38846,7 +39111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B127"/>
+  <dimension ref="A1:B128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -39870,6 +40135,14 @@
       </c>
       <c r="B127" t="n">
         <v>21.4</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B128" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -39884,7 +40157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B131"/>
+  <dimension ref="A1:B132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -40940,6 +41213,14 @@
       </c>
       <c r="B131" t="n">
         <v>943.8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>829.4</v>
       </c>
     </row>
   </sheetData>
@@ -40954,7 +41235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -43718,6 +43999,29 @@
       </c>
       <c r="G131" t="n">
         <v>-0.8</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E132" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="F132" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G132" t="n">
+        <v>-1.2</v>
       </c>
     </row>
   </sheetData>
@@ -43732,7 +44036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -46301,6 +46605,26 @@
         <v>0.8</v>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B132" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E132" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
